--- a/artfynd/A 23793-2026 artfynd.xlsx
+++ b/artfynd/A 23793-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134147329</v>
       </c>
       <c r="B2" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>134152224</v>
       </c>
       <c r="B3" t="n">
-        <v>96494</v>
+        <v>96504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>134152315</v>
       </c>
       <c r="B4" t="n">
-        <v>96494</v>
+        <v>96504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>134147307</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23793-2026 artfynd.xlsx
+++ b/artfynd/A 23793-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134147329</v>
+        <v>134193163</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354002</v>
+        <v>353697</v>
       </c>
       <c r="R2" t="n">
-        <v>6606400</v>
+        <v>6606576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,13 +752,17 @@
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -770,39 +774,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134152224</v>
+        <v>134147329</v>
       </c>
       <c r="B3" t="n">
-        <v>96504</v>
+        <v>98043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1079</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353855</v>
+        <v>354002</v>
       </c>
       <c r="R3" t="n">
-        <v>6606410</v>
+        <v>6606400</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,27 +862,12 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -887,14 +876,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Granback, Lars-Inge Hedlund</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134152315</v>
+        <v>134152224</v>
       </c>
       <c r="B4" t="n">
         <v>96504</v>
@@ -933,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353801</v>
+        <v>353855</v>
       </c>
       <c r="R4" t="n">
-        <v>6606429</v>
+        <v>6606410</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,6 +969,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,42 +1000,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134147307</v>
+        <v>134152315</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>96504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>354000</v>
+        <v>353801</v>
       </c>
       <c r="R5" t="n">
-        <v>6606417</v>
+        <v>6606429</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,8 +1081,9 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,10 +1095,115 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Jesper Granback, Lars-Inge Hedlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134147307</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stretsbol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>354000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6606417</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Jesper Granback</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23793-2026 artfynd.xlsx
+++ b/artfynd/A 23793-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>134147329</v>
       </c>
       <c r="B3" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>134152224</v>
       </c>
       <c r="B4" t="n">
-        <v>96504</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>134152315</v>
       </c>
       <c r="B5" t="n">
-        <v>96504</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23793-2026 artfynd.xlsx
+++ b/artfynd/A 23793-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>134147329</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>134152224</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>134152315</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23793-2026 artfynd.xlsx
+++ b/artfynd/A 23793-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134193163</v>
+        <v>134152224</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>96521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353697</v>
+        <v>353855</v>
       </c>
       <c r="R2" t="n">
-        <v>6606576</v>
+        <v>6606410</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +752,30 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -774,39 +785,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Granback, Lisa Ingwall-King</t>
+          <t>Jesper Granback, Lars-Inge Hedlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134147329</v>
+        <v>134152315</v>
       </c>
       <c r="B3" t="n">
-        <v>98053</v>
+        <v>96521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>354002</v>
+        <v>353801</v>
       </c>
       <c r="R3" t="n">
-        <v>6606400</v>
+        <v>6606429</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -876,45 +887,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Lars-Inge Hedlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134152224</v>
+        <v>134147234</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1079</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -922,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353855</v>
+        <v>353874</v>
       </c>
       <c r="R4" t="n">
-        <v>6606410</v>
+        <v>6606458</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,26 +979,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -993,45 +992,49 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Granback, Lars-Inge Hedlund</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134152315</v>
+        <v>134147307</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1079</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>353801</v>
+        <v>354000</v>
       </c>
       <c r="R5" t="n">
-        <v>6606429</v>
+        <v>6606417</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1084,8 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,21 +1097,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Granback, Lars-Inge Hedlund</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134147307</v>
+        <v>134147541</v>
       </c>
       <c r="B6" t="n">
         <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1145,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>354000</v>
+        <v>353682</v>
       </c>
       <c r="R6" t="n">
-        <v>6606417</v>
+        <v>6606665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1206,214 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134193163</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stretsbol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>353697</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6606576</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Granback, Lisa Ingwall-King</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134147329</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stretsbol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>354002</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6606400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
